--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -11143,7 +11143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -11666,7 +11666,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>№ 434-001.001/002.0/17-26 від 11.09.2026</t>
+          <t>№ 434-001.001/002.0 17-26 від 11.09.2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -11676,7 +11676,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>DYSPORT® 500 U (Botulinum toxin type A), ліофілізований порошок, Серія № P08193, з маркуванням Ipsen Farmaceutica Ltda, -</t>
+          <t>СТРЕПСІЛС® З ВІТАМІНОМ С ЗІ СМАКОМ АПЕЛЬСИНА, льодяники, по 12 льодяників у блістері; по 2 блістери в картонній коробці, Серія № ST420, Реккітт Бенкізер Хелскер Інтернешнл Лімітед, Велика Британiя</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -11687,6 +11687,34 @@
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19" ht="40" customHeight="1">
+      <c r="A19" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>№ 434-001.001/002.0/17-26 від 11.09.2026</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>11.09.2026</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>DYSPORT® 500 U (Botulinum toxin type A), ліофілізований порошок, Серія № P08193, з маркуванням Ipsen Farmaceutica Ltda, -</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -11143,7 +11143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -11716,6 +11716,90 @@
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr"/>
     </row>
+    <row r="20" ht="40" customHeight="1">
+      <c r="A20" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>№ 435-001.001/002.0/17-26 від 15.09.2026</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>15.09.2026</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>НІМЕСУЛІД, порошок (субстанція) у подвійних пакетах з поліетилену для фармацевтичного застосування, Серія № NMS/125010052, Аарті Драгз Лімітед, Індія</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21" ht="40" customHeight="1">
+      <c r="A21" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>№ 436-001.001/002.0/17-26 від 15.09.2026</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>15.09.2026</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>TERZAPOWER 60 mg/Vial (Tirzepatide), ліофілізований порошок, флакон у картонній коробці, Серія № всі серії, з маркуванням TRUE MED Ukraine, -</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>№ 437-001.001/002.0/17-26 від 15.09.2026</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>15.09.2026</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>TERZAPOWER 20 mg (Tirzepatide),20 mg/3 ml, 1 ручка-аплікатор у картонній коробці, Серія № всі серії, з маркуванням виробника Трумед Юкрайн, Корея</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -11143,7 +11143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -11246,7 +11246,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>№ 419-001.001/002.0/17-26 від 09.09.2026</t>
+          <t>№ 420-001.001/002.0/17-26 від 09.09.2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -11256,7 +11256,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>ІБУПРОФЕН Б.БРАУН, розчин для інфузій, 400 мг/100 мл по 100 мл у поліетиленових флаконах, по 100 мл у поліетиленових флаконах, по 10 або 20 флаконів у картонній коробці, Серія № всі серії, Б. Браун Медікал СА, Іспанія</t>
+          <t>DUTILOX (Duloxetinum), кишковорозчинні капсули, тверді, № 30, № 60, Серія № всі серії, TOWA Pharmaceutical Europe S.L.C, Іспанія</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -11274,7 +11274,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>№ 420-001.001/002.0/17-26 від 09.09.2026</t>
+          <t>№ 421-001.001/002.0/17-26 від 09.09.2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>DUTILOX (Duloxetinum), кишковорозчинні капсули, тверді, № 30, № 60, Серія № всі серії, TOWA Pharmaceutical Europe S.L.C, Іспанія</t>
+          <t>FINGOLIMOD ZENTIVA (Fingolimodum) 0,5 mg, капсули в блістері № 28, Серія № 4L01372M (bulk: 4L01372), LABORMED-PHARMA S.A., Румунія</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -11302,7 +11302,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>№ 421-001.001/002.0/17-26 від 09.09.2026</t>
+          <t>№ 422-001.001/002.0/17-26 від 09.09.2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>FINGOLIMOD ZENTIVA (Fingolimodum) 0,5 mg, капсули в блістері № 28, Серія № 4L01372M (bulk: 4L01372), LABORMED-PHARMA S.A., Румунія</t>
+          <t>CUREOUS Cannabis- flower BLB THC32, 150 g, Серія № B15F125, ECO GROW s.r.o., -</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -11330,7 +11330,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>№ 422-001.001/002.0/17-26 від 09.09.2026</t>
+          <t>№ 423-001.001/002.0/17-26 від 09.09.2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>CUREOUS Cannabis- flower BLB THC32, 150 g, Серія № B15F125, ECO GROW s.r.o., -</t>
+          <t>АБІЗОЛ, розчин оральний 1 мг/мл, по 150 мл розчину у флаконі, по одному флакону з мірним стаканчиком та шприцом-дозатором у картонній упаковці, Серія № ECVG002A, НОБЕЛ ІЛАЧ САНАЇ ВЕ ТІДЖАРЕТ А.Ш., Туреччина</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -11358,7 +11358,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>№ 423-001.001/002.0/17-26 від 09.09.2026</t>
+          <t>№ 424-001.001/002.0/17-26 від 09.09.2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -11368,7 +11368,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>АБІЗОЛ, розчин оральний 1 мг/мл, по 150 мл розчину у флаконі, по одному флакону з мірним стаканчиком та шприцом-дозатором у картонній упаковці, Серія № ECVG002A, НОБЕЛ ІЛАЧ САНАЇ ВЕ ТІДЖАРЕТ А.Ш., Туреччина</t>
+          <t>БРУФЕН® РАПІД, капсули м'які по 400 мг, по 10 капсул у блістері, по 1 блістеру у картонній коробці, Серія № B4U00225, Гелтек Прайвет Лімітед, Індія</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -11386,7 +11386,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>№ 424-001.001/002.0/17-26 від 09.09.2026</t>
+          <t>№ 425-001.001/002.0/17-26 від 09.09.2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -11396,7 +11396,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>БРУФЕН® РАПІД, капсули м'які по 400 мг, по 10 капсул у блістері, по 1 блістеру у картонній коробці, Серія № B4U00225, Гелтек Прайвет Лімітед, Індія</t>
+          <t>НЕЙРОДАР®, таблетки, вкриті оболонкою, по 500 мг, по 10 таблеток у блістері; по 1 блістеру в картонній упаковці; по 3  упаковки у картонній коробці, Серія № 1008952, Кусум Хелтхкер Пвт Лтд, Індія</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -11414,7 +11414,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>№ 425-001.001/002.0/17-26 від 09.09.2026</t>
+          <t>№ 426-001.001/002.0/17-26 від 09.09.2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -11424,7 +11424,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>НЕЙРОДАР®, таблетки, вкриті оболонкою, по 500 мг, по 10 таблеток у блістері; по 1 блістеру в картонній упаковці; по 3  упаковки у картонній коробці, Серія № 1008952, Кусум Хелтхкер Пвт Лтд, Індія</t>
+          <t>MONASAN INJECTION 1ml Ampoule (Fluphenazine Decanoate), 25 мг/мл в ампулі зі скла бурштинового кольору типу I, Серія № 250879, 251988, Duopharma (M) Sendirian Berhad, Малайзія</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -11442,17 +11442,17 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>№ 426-001.001/002.0/17-26 від 09.09.2026</t>
+          <t>№ 427-001.001/002.0/17-26 від 10.09.2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>10.09.2026</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>MONASAN INJECTION 1ml Ampoule (Fluphenazine Decanoate), 25 мг/мл в ампулі зі скла бурштинового кольору типу I, Серія № 250879, 251988, Duopharma (M) Sendirian Berhad, Малайзія</t>
+          <t>БОТОКС/BOTOX 100 units, БОТОКС/BOTOX 100 units, порошок для розчину для ін’єкцій у флаконі у картонній коробці, Серія № С3822 С3, з маркуванням Аллерган Фармасьютікалз, -</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -11470,7 +11470,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>№ 427-001.001/002.0/17-26 від 10.09.2026</t>
+          <t>№ 428-001.001/002.0/17-26 від 10.09.2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -11480,7 +11480,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>БОТОКС/BOTOX 100 units, БОТОКС/BOTOX 100 units, порошок для розчину для ін’єкцій у флаконі у картонній коробці, Серія № С3822 С3, з маркуванням Аллерган Фармасьютікалз, -</t>
+          <t>КРЕСТОР, таблетки, вкриті плівковою оболонкою, по 20 мг; по 14 таблеток у блістері; по 2 блістери в картонній коробці, Серія № А26237002, А25237040, АстраЗенека ЮК Лімітед, Велика Британія, США/ Велика Британія</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -11498,7 +11498,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>№ 428-001.001/002.0/17-26 від 10.09.2026</t>
+          <t>№ 429-001.001/002.0/17-26 від 10.09.2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -11508,7 +11508,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>КРЕСТОР, таблетки, вкриті плівковою оболонкою, по 20 мг; по 14 таблеток у блістері; по 2 блістери в картонній коробці, Серія № А26237002, А25237040, АстраЗенека ЮК Лімітед, Велика Британія, США/ Велика Британія</t>
+          <t>DARZALEX (Daratumumab), 400 mg/20 ml, концентрат для розчину для інфузій, флакон 20 мл, Серія № SLF4S40, з маркуванням Janssen, -</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -11526,7 +11526,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>№ 429-001.001/002.0/17-26 від 10.09.2026</t>
+          <t>№ 430-001.001/002.0/17-26 від 10.09.2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -11536,7 +11536,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>DARZALEX (Daratumumab), 400 mg/20 ml, концентрат для розчину для інфузій, флакон 20 мл, Серія № SLF4S40, з маркуванням Janssen, -</t>
+          <t>OZEMPIC 1MG 1PC. W. NF+ 4PCS. (Semaglutidum), розчин для ін'єкцій у попередньо заповненій шприц-ручці, Серія № RT6KL87, з маркуванням виробника Novo Nordisk A/S., -</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -11554,17 +11554,17 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>№ 430-001.001/002.0/17-26 від 10.09.2026</t>
+          <t>№ 431-001.001/002.0/17-26 від 11.09.2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>10.09.2026</t>
+          <t>11.09.2026</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>OZEMPIC 1MG 1PC. W. NF+ 4PCS. (Semaglutidum), розчин для ін'єкцій у попередньо заповненій шприц-ручці, Серія № RT6KL87, з маркуванням виробника Novo Nordisk A/S., -</t>
+          <t>СТРЕПСІЛС® З ВІТАМІНОМ С ЗІ СМАКОМ АПЕЛЬСИНА, льодяники, по 12 льодяників у блістері; по 2 блістери в картонній коробці, Серія № ST420, Реккітт Бенкізер Хелскер Інтернешнл Лімітед, Велика Британiя</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -11582,7 +11582,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>№ 431-001.001/002.0/17-26 від 11.09.2026</t>
+          <t>№ 432-001.001/002.0/17-26 від 11.09.2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -11592,7 +11592,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>СТРЕПСІЛС® З ВІТАМІНОМ С ЗІ СМАКОМ АПЕЛЬСИНА, льодяники, по 12 льодяників у блістері; по 2 блістери в картонній коробці, Серія № ST420, Реккітт Бенкізер Хелскер Інтернешнл Лімітед, Велика Британiя</t>
+          <t>всі ЛЗ виробництва Xi’an Guokang Ruijin Pharmaceutical co. Ltd, -, Серія № всі серії, Xi’an Guokang Ruijin Pharmaceutical co. Ltd, Китай</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -11610,7 +11610,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>№ 432-001.001/002.0/17-26 від 11.09.2026</t>
+          <t>№ 433-001.001/002.0/17-26 від 11.09.2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -11620,7 +11620,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>всі ЛЗ виробництва Xi’an Guokang Ruijin Pharmaceutical co. Ltd, -, Серія № всі серії, Xi’an Guokang Ruijin Pharmaceutical co. Ltd, Китай</t>
+          <t>АСКОЦИН®, таблетки жувальні; по 10 таблеток у стрипі; по 10 стрипів у картонній упаковці, Серія № 1004650, КУСУМ ХЕЛТХКЕР ПВТ ЛТД, Індія</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -11638,7 +11638,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>№ 433-001.001/002.0/17-26 від 11.09.2026</t>
+          <t>№ 434-001.001/002.0 17-26 від 11.09.2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -11648,7 +11648,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>АСКОЦИН®, таблетки жувальні; по 10 таблеток у стрипі; по 10 стрипів у картонній упаковці, Серія № 1004650, КУСУМ ХЕЛТХКЕР ПВТ ЛТД, Індія</t>
+          <t>СТРЕПСІЛС® З ВІТАМІНОМ С ЗІ СМАКОМ АПЕЛЬСИНА, льодяники, по 12 льодяників у блістері; по 2 блістери в картонній коробці, Серія № ST420, Реккітт Бенкізер Хелскер Інтернешнл Лімітед, Велика Британiя</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -11666,7 +11666,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>№ 434-001.001/002.0 17-26 від 11.09.2026</t>
+          <t>№ 434-001.001/002.0/17-26 від 11.09.2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -11676,7 +11676,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>СТРЕПСІЛС® З ВІТАМІНОМ С ЗІ СМАКОМ АПЕЛЬСИНА, льодяники, по 12 льодяників у блістері; по 2 блістери в картонній коробці, Серія № ST420, Реккітт Бенкізер Хелскер Інтернешнл Лімітед, Велика Британiя</t>
+          <t>DYSPORT® 500 U (Botulinum toxin type A), ліофілізований порошок, Серія № P08193, з маркуванням Ipsen Farmaceutica Ltda, -</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -11694,17 +11694,17 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>№ 434-001.001/002.0/17-26 від 11.09.2026</t>
+          <t>№ 435-001.001/002.0/17-26 від 15.09.2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>11.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>DYSPORT® 500 U (Botulinum toxin type A), ліофілізований порошок, Серія № P08193, з маркуванням Ipsen Farmaceutica Ltda, -</t>
+          <t>НІМЕСУЛІД, порошок (субстанція) у подвійних пакетах з поліетилену для фармацевтичного застосування, Серія № NMS/125010052, Аарті Драгз Лімітед, Індія</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -11722,7 +11722,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>№ 435-001.001/002.0/17-26 від 15.09.2026</t>
+          <t>№ 436-001.001/002.0/17-26 від 15.09.2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -11732,7 +11732,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>НІМЕСУЛІД, порошок (субстанція) у подвійних пакетах з поліетилену для фармацевтичного застосування, Серія № NMS/125010052, Аарті Драгз Лімітед, Індія</t>
+          <t>TERZAPOWER 60 mg/Vial (Tirzepatide), ліофілізований порошок, флакон у картонній коробці, Серія № всі серії, з маркуванням TRUE MED Ukraine, -</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -11750,7 +11750,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>№ 436-001.001/002.0/17-26 від 15.09.2026</t>
+          <t>№ 437-001.001/002.0/17-26 від 15.09.2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -11760,7 +11760,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>TERZAPOWER 60 mg/Vial (Tirzepatide), ліофілізований порошок, флакон у картонній коробці, Серія № всі серії, з маркуванням TRUE MED Ukraine, -</t>
+          <t>TERZAPOWER 20 mg (Tirzepatide),20 mg/3 ml, 1 ручка-аплікатор у картонній коробці, Серія № всі серії, з маркуванням виробника Трумед Юкрайн, Корея</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -11778,17 +11778,17 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>№ 437-001.001/002.0/17-26 від 15.09.2026</t>
+          <t>№ 438-001.001/002.0/17-26 від 16.09.2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>TERZAPOWER 20 mg (Tirzepatide),20 mg/3 ml, 1 ручка-аплікатор у картонній коробці, Серія № всі серії, з маркуванням виробника Трумед Юкрайн, Корея</t>
+          <t>TWINCRET® (TIRZEPATIDE) 20 mg, 20mg/3ml ручка-аплікатор має фірмову картонну коробку SunSci з написом: «Twincret Tirzepatide» 20mg/3ml, «1 pre-filled pen», в середині якої знаходилась ручка-аплікатор білого кольору з наступною інформацією: «Twincret Tirzepatide» 20mg/3ml «GIP and GLP-1, Серія № всі серії, з маркуванням SunSci, -</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -11799,6 +11799,118 @@
       <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>№ 439-001.001/002.0/17-26 від 16.09.2026</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>16.09.2026</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>PEN PEPTIDE BIOPATID 2 ml 20 mg  (TIRZEPATIDE), шприц-ручка у картонній коробці, Серія № всі серії, з маркуванням виробників HOMNEM CLINIC COMERCIO, UNIKKA PHARMA LTD, Бразилія</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>№ 440-001.001/002.0/17-26 від 16.09.2026</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>16.09.2026</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>BIOPATID KIT 2 ml 10 mg (TIRZEPATIDE), 1 шприц-ручка та 6 флаконів у картонній коробці, Серія № всі серії, з маркуванням виробника UNIKKA PHARMA LTD, Бразилія</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>№ 441-001.001/002.0/17-26 від 16.09.2026</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>16.09.2026</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>BIOPATID 2 ml 20mg (TIRZEPATIDE), флакон у картонній коробці, Серія № всі серії, з маркуванням виробника HOMNEM CLINIC COMERCIO, -</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26" ht="40" customHeight="1">
+      <c r="A26" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>№ 441-001.001/002.0/17-26 від 16.09.2026</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>16.09.2026</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>BIOPATID 2 ml 60 mg (TIRZEPATIDE), флакон у картонній коробці, Серія № всі серії, з маркуванням виробника HOMNEM CLINIC COMERCIO, Бразилія</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -11143,7 +11143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -11912,6 +11912,34 @@
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr"/>
     </row>
+    <row r="27" ht="40" customHeight="1">
+      <c r="A27" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>№ 444-001.001/002.0/17-26 від 18.09.2026</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>18.09.2026</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>КЛІМАКТО-ГРАН, гранули, по 5 г гранул у контейнері з дозуванням, по 2 контейнери в пачці з картону, Серія № 001 1024, ПрАТ «Національна Гомеопатична Спілка», Україна</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -7063,7 +7063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8240,7 +8240,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>ЦЕФОТРИН, порошок для розчину для ін’єкцій по 1 г, 1 флакон з порошком в картонній коробці, Серія № 33260502, 33260503, 33260504, 33260302, 33260203, 33260301, 33260501, 33260202, 33250902, 33250901, 33241101, 33241203, 33241201, 33241202, 33241102, 33241103, 33240801, 33240802, 33240601, 33240602, 3322113, Ананта Медікеар Лімітед, Індія, Індія</t>
+          <t>ЦЕФЕПІМ АНАНТА, порошок для розчину для ін'єкцій по 2 г; 1 або 10 флаконів з порошком в коробці, Серія № всі серії, Ананта Медікеар Лімітед, Індія</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>ЦЕФЕПІМ АНАНТА, порошок для розчину для ін'єкцій по 2 г; 1 або 10 флаконів з порошком в коробці, Серія № всі серії, Ананта Медікеар Лімітед, Індія</t>
+          <t>ЦЕФЕПІМ АНАНТА, порошок для розчину для ін'єкцій по 1 г; 1 або 10 флаконів з порошком в коробці, Серія № всі серії, Ананта Медікеар Лімітед, Індія</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>ЦЕФЕПІМ АНАНТА, порошок для розчину для ін'єкцій по 1 г; 1 або 10 флаконів з порошком в коробці, Серія № всі серії, Ананта Медікеар Лімітед, Індія</t>
+          <t>ФЛОРАЗІД, порошок для розчину для ін`єкцій по 2 г, 1 флакон з порошком у коробці, Серія № всі серії, Ананта Медікеар Лімітед, Індія, Індія</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>ФЛОРАЗІД, порошок для розчину для ін`єкцій по 2 г, 1 флакон з порошком у коробці, Серія № всі серії, Ананта Медікеар Лімітед, Індія, Індія</t>
+          <t>ФОРЦЕФТРИН, порошок для розчину для ін'єкцій по 1,5 г у флаконі, по 1 флакону з порошком у коробці, Серія № всі серії, Ананта Медікеар Лімітед, Індія</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -8342,17 +8342,17 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>№ 335-001.001/002.0/17-26 від 22.07.2026</t>
+          <t>№ 336-001.001/002.0/17-26 від 24.07.2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>22.07.2026</t>
+          <t>24.07.2026</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>ФОРЦЕФТРИН, порошок для розчину для ін'єкцій по 1,5 г у флаконі, по 1 флакону з порошком у коробці, Серія № всі серії, Ананта Медікеар Лімітед, Індія</t>
+          <t>ПАКЛІТАКСЕЛ АМАКСА, концентрат для розчину для інфузій, 6 мг/мл; по 5 мл, 16,7 мл або 50 мл у флаконі; по 1 флакону в картонній коробці, Серія № AO261002, контроль та випуск серії: АкВіда ГмбХ, Німеччина виробництво in bulk, первинне та вторинне пакування: Самянг Холдінгз Корпорейшн, Республiка Корея виробництво in bulk, первинне пакування, вторинне пакування, контроль серії: АкВіда ГмбХ, Німеччина, Німеччина/ Республiка Корея</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -8370,17 +8370,17 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>№ 336-001.001/002.0/17-26 від 24.07.2026</t>
+          <t>№ 337-001.001/002.0/17-26 від 27.07.2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>24.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>ПАКЛІТАКСЕЛ АМАКСА, концентрат для розчину для інфузій, 6 мг/мл; по 5 мл, 16,7 мл або 50 мл у флаконі; по 1 флакону в картонній коробці, Серія № AO261002, контроль та випуск серії: АкВіда ГмбХ, Німеччина виробництво in bulk, первинне та вторинне пакування: Самянг Холдінгз Корпорейшн, Республiка Корея виробництво in bulk, первинне пакування, вторинне пакування, контроль серії: АкВіда ГмбХ, Німеччина, Німеччина/ Республiка Корея</t>
+          <t>ЛОПЕРАМІД, таблетки по 2 мг по 10 таблеток у блістері; по 2 блістери в пачці, Серія № 011188, ТОВ "МАРІФАРМ", Словенія</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -8398,7 +8398,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>№ 337-001.001/002.0/17-26 від 27.07.2026</t>
+          <t>№ 338-001.001/002.0/17-26 від 27.07.2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -8408,7 +8408,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>ЛОПЕРАМІД, таблетки по 2 мг по 10 таблеток у блістері; по 2 блістери в пачці, Серія № 011188, ТОВ "МАРІФАРМ", Словенія</t>
+          <t>ГРИПОМЕД®, капсули, по 10 капсул у блістері; по 2 блістери у пачці з картону, Серія № 070925, ПАТ "Хімфармзавод "Червона зірка", Україна</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>№ 338-001.001/002.0/17-26 від 27.07.2026</t>
+          <t>№ 339-001.001/002.0/17-26 від 27.07.2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>ГРИПОМЕД®, капсули, по 10 капсул у блістері; по 2 блістери у пачці з картону, Серія № 070925, ПАТ "Хімфармзавод "Червона зірка", Україна</t>
+          <t>ГАБАНА®, капсули по 300 мг, по 10 капсул у блістері; по 2 блістери в пачці, Серія № 011523, ТОВ «МАРІФАРМ», Словенія</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -8464,7 +8464,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>ГАБАНА®, капсули по 300 мг, по 10 капсул у блістері; по 2 блістери в пачці, Серія № 011523, ТОВ «МАРІФАРМ», Словенія</t>
+          <t>ГАБАНА®, капсули по 300 мг, по 10 капсул у блістері; по 2 блістери в пачці, Серія № 011520, ТОВ «МАРІФАРМ», Словенія</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -8492,7 +8492,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>ГАБАНА®, капсули по 300 мг, по 10 капсул у блістері; по 2 блістери в пачці, Серія № 011520, ТОВ «МАРІФАРМ», Словенія</t>
+          <t>ГАБАНА®, капсули по 300 мг, по 10 капсул у блістері; по 2 блістери в пачці, Серія № 011502, ТОВ «МАРІФАРМ», Словенія</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>№ 339-001.001/002.0/17-26 від 27.07.2026</t>
+          <t>№ 342-001.001/002.0/17-26 від 27.07.2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>ГАБАНА®, капсули по 300 мг, по 10 капсул у блістері; по 2 блістери в пачці, Серія № 011502, ТОВ «МАРІФАРМ», Словенія</t>
+          <t>САЛІЦИЛОВА МАЗЬ, мазь 10 % по 25 г у тубі ламінатній в пачці, Серія № 010124, ПрАТ Фармацевтична фабрика "Віола", Україна</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -8548,7 +8548,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>САЛІЦИЛОВА МАЗЬ, мазь 10 % по 25 г у тубі ламінатній в пачці, Серія № 010124, ПрАТ Фармацевтична фабрика "Віола", Україна</t>
+          <t>САЛІЦИЛОВА МАЗЬ, мазь 10% по 25 г у тубі ламінатній в пачці, Серія № 090824, ПрАТ Фармацевтична фабрика "Віола", Україна</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -8576,7 +8576,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>САЛІЦИЛОВА МАЗЬ, мазь 10% по 25 г у тубі ламінатній в пачці, Серія № 090824, ПрАТ Фармацевтична фабрика "Віола", Україна</t>
+          <t>САЛІЦИЛОВА МАЗЬ, мазь 10 % по 25 г у тубі ламінатній; по 1 тубі в пачці, Серія № 111023, ПрАТ Фармацевтична фабрика "Віола", Україна</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -8594,17 +8594,17 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>№ 342-001.001/002.0/17-26 від 27.07.2026</t>
+          <t>№ 343-001.001/002.0/17-26 від 28.07.2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>28.07.2026</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>САЛІЦИЛОВА МАЗЬ, мазь 10 % по 25 г у тубі ламінатній; по 1 тубі в пачці, Серія № 111023, ПрАТ Фармацевтична фабрика "Віола", Україна</t>
+          <t>ЕМЛА, крем по 30 г у тубі; по 1 тубі у картонній коробці, Серія № 100272, Ресіфарм Карлскога АБ, Австрія</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -8622,7 +8622,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>№ 343-001.001/002.0/17-26 від 28.07.2026</t>
+          <t>№ 344-001.001/002.0/17-26 від 28.07.2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -8632,7 +8632,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>ЕМЛА, крем по 30 г у тубі; по 1 тубі у картонній коробці, Серія № 100272, Ресіфарм Карлскога АБ, Австрія</t>
+          <t>VALAMOR (ribociclib) 200 mg, таблетки № 63, Серія № A0213K, Novartis Sagl?k, G?da ve Tar?m Urunleri San. ve Tic. A.S., -</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -8650,7 +8650,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>№ 344-001.001/002.0/17-26 від 28.07.2026</t>
+          <t>№ 345-001.001/002.0/17-26 від 28.07.2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -8660,7 +8660,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>VALAMOR (ribociclib) 200 mg, таблетки № 63, Серія № A0213K, Novartis Sagl?k, G?da ve Tar?m Urunleri San. ve Tic. A.S., -</t>
+          <t>ФІБРИНАЗА-20, таблетки, вкриті оболонкою, кишковорозчинні по 20 мг; по 10 таблеток у блістері; по 3 блістери у картонній пачці, Серія № EBK25010B1, EBK25011B1, EBK25012B1, EBK26004B1, EBK26005B1, EBK26007B1, Евертоджен Лайф Саєнсиз  Лімітед, Індія</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -8688,7 +8688,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>ФІБРИНАЗА-20, таблетки, вкриті оболонкою, кишковорозчинні по 20 мг; по 10 таблеток у блістері; по 3 блістери у картонній пачці, Серія № EBK25010B1, EBK25011B1, EBK25012B1, EBK26004B1, EBK26005B1, EBK26007B1, Евертоджен Лайф Саєнсиз  Лімітед, Індія</t>
+          <t>ФІБРИНАЗА-10, таблетки, вкриті оболонкою, кишковорозчинні по 10 мг, по 10 таблеток у блістері; по 3 блістери у картонній пачці, Серія № ESI25011B1, ESI25012B1, ESI26002B1, ESI26003B1, Евертоджен Лайф Саєнсиз Лімітед, Індія</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -8706,17 +8706,17 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>№ 345-001.001/002.0/17-26 від 28.07.2026</t>
+          <t>№ 346-001.001/002.0/17-26 від 29.07.2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>28.07.2026</t>
+          <t>29.07.2026</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>ФІБРИНАЗА-10, таблетки, вкриті оболонкою, кишковорозчинні по 10 мг, по 10 таблеток у блістері; по 3 блістери у картонній пачці, Серія № ESI25011B1, ESI25012B1, ESI26002B1, ESI26003B1, Евертоджен Лайф Саєнсиз Лімітед, Індія</t>
+          <t>ЦИТРАМОН В, таблетки;  по  10 таблеток у блістерах, Серія № 61025, ПАТ "Монфарм", Україна</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -8734,7 +8734,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>№ 346-001.001/002.0/17-26 від 29.07.2026</t>
+          <t>№ 348-001.001/002.0/17-26 від 29.07.2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -8744,7 +8744,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>ЦИТРАМОН В, таблетки;  по  10 таблеток у блістерах, Серія № 61025, ПАТ "Монфарм", Україна</t>
+          <t>СЕПТАНЕСТ З АДРЕНАЛІНОМ 1/100 000, розчин для ін'єкцій по 1,7 мл у картриджі; по 10 картриджів у блістері; по 5 блістерів у картонній коробці, Серія № L00609BA, СЕПТОДОНТ, Франція</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -8772,7 +8772,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>СЕПТАНЕСТ З АДРЕНАЛІНОМ 1/100 000, розчин для ін'єкцій по 1,7 мл у картриджі; по 10 картриджів у блістері; по 5 блістерів у картонній коробці, Серія № L00609BA, СЕПТОДОНТ, Франція</t>
+          <t>СЕПТАНЕСТ З АДРЕНАЛІНОМ 1/200 000, розчин для ін'єкцій по 1,7 мл у картриджі; по 10 картриджів у блістері; по 5 блістерів у картонній коробці, Серія № L00611AC, СЕПТОДОНТ, Франція</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -8790,17 +8790,17 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>№ 348-001.001/002.0/17-26 від 29.07.2026</t>
+          <t>№ 349-001.001/002.0/17-26 від 30.07.2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>29.07.2026</t>
+          <t>30.07.2026</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>СЕПТАНЕСТ З АДРЕНАЛІНОМ 1/200 000, розчин для ін'єкцій по 1,7 мл у картриджі; по 10 картриджів у блістері; по 5 блістерів у картонній коробці, Серія № L00611AC, СЕПТОДОНТ, Франція</t>
+          <t>СЕПТАНЕСТ З АДРЕНАЛІНОМ 1/100 000, розчин для ін'єкцій по 1,7 мл у картриджі; по 10 картриджів у блістері; по 5 блістерів у картонній коробці, Серія № L00609BA, СЕПТОДОНТ, Франція</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -8818,17 +8818,17 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>№ 349-001.001/002.0/17-26 від 30.07.2026</t>
+          <t>№ 351-001.001/002.0/17-26 від 31.07.2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>30.07.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>СЕПТАНЕСТ З АДРЕНАЛІНОМ 1/100 000, розчин для ін'єкцій по 1,7 мл у картриджі; по 10 картриджів у блістері; по 5 блістерів у картонній коробці, Серія № L00609BA, СЕПТОДОНТ, Франція</t>
+          <t>ДРОТАВЕРИНУ ГІДРОХЛОРИД, таблетки по 40 мг; по 10 таблеток у блістері; по 2 блістера в пачці з картону, Серія № 40126, АТ "Лубнифарм", Україна</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -8846,7 +8846,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>№ 351-001.001/002.0/17-26 від 31.07.2026</t>
+          <t>№ 353-001.001/002.0/17-26 від 31.07.2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -8856,7 +8856,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>ДРОТАВЕРИНУ ГІДРОХЛОРИД, таблетки по 40 мг; по 10 таблеток у блістері; по 2 блістера в пачці з картону, Серія № 40126, АТ "Лубнифарм", Україна</t>
+          <t>всі серії ЛЗ виробництва LIANYUNGANG GUIKE PHARMACEUTICAL CO. LTD., -, Серія № всі серії, LIANYUNGANG GUIKE PHARMACEUTICAL CO. LTD., Китай</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -8867,34 +8867,6 @@
       <c r="F63" s="2" t="inlineStr"/>
       <c r="G63" s="2" t="inlineStr"/>
       <c r="H63" s="2" t="inlineStr"/>
-    </row>
-    <row r="64" ht="40" customHeight="1">
-      <c r="A64" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>№ 353-001.001/002.0/17-26 від 31.07.2026</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>31.07.2026</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>всі серії ЛЗ виробництва LIANYUNGANG GUIKE PHARMACEUTICAL CO. LTD., -, Серія № всі серії, LIANYUNGANG GUIKE PHARMACEUTICAL CO. LTD., Китай</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>відсутній</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr"/>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11143,7 +11115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -11940,6 +11912,146 @@
       <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="2" t="inlineStr"/>
     </row>
+    <row r="28" ht="40" customHeight="1">
+      <c r="A28" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>№ 445-001.001/002.0/17-26 від 21.09.2026</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>21.09.2026</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>PEN PEPTIDE BIOPATID 2 ml 20 mg  (TIRZEPATIDE), шприц-ручка у картонній коробці, Серія № всі серії, з маркуванням виробників HOMNEM CLINIC COMERCIO, UNIKKA PHARMA LTD, Бразилія</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29" ht="40" customHeight="1">
+      <c r="A29" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>№ 447-001.001/002.0/17-26 від 21.09.2026</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>21.09.2026</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>TERZAPOWER 60 mg/Vial (Tirzepatide), ліофілізований порошок, флакон у картонній коробці, Серія № всі серії, з маркуванням TRUE MED Ukraine, -</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30" ht="40" customHeight="1">
+      <c r="A30" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>№ 447-001.001/002.0/17-26 від 21.09.2026</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>21.09.2026</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>TERZAPOWER 20 mg (Tirzepatide),20 mg/3 ml, 1 ручка-аплікатор у картонній коробці, Серія № всі серії, з маркуванням виробника Трумед Юкрайн, Корея</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31" ht="40" customHeight="1">
+      <c r="A31" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>№ 448-001.001/002.0/17-26 від 21.09.2026</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>21.09.2026</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>BIOPATID 2 ml 20mg (TIRZEPATIDE), флакон у картонній коробці, Серія № всі серії, з маркуванням виробника HOMNEM CLINIC COMERCIO, -</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32" ht="40" customHeight="1">
+      <c r="A32" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>№ 448-001.001/002.0/17-26 від 21.09.2026</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>21.09.2026</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>BIOPATID 2 ml 60 mg (TIRZEPATIDE), флакон у картонній коробці, Серія № всі серії, з маркуванням виробника HOMNEM CLINIC COMERCIO, Бразилія</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -11115,7 +11115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -12052,6 +12052,34 @@
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr"/>
     </row>
+    <row r="33" ht="40" customHeight="1">
+      <c r="A33" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>№ 456-001.001/002.0/17-26 від 23.09.2026</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>23.09.2026</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>КЕТОРОЛ ГЕЛЬ, гель 2 % по 30 г у тубі; по 1 тубі в коробці, Серія № V260401, Д-р Редді'с Лабораторіс Лімітед, Індія</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -11115,7 +11115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -12080,6 +12080,34 @@
       <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr"/>
     </row>
+    <row r="34" ht="40" customHeight="1">
+      <c r="A34" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>№ 457-001.001/002.0/17-26 від 24.09.2026</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>24.09.2026</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>ТОБРАДЕКС®, мазь очна по 3,5 г у тубі; по 1 тубі у коробці з картону, Серія № VDM61B, VFE07A, VLL71A, Новартіс Мануфактурінг НВ, Бельгiя</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -11115,7 +11115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -12108,6 +12108,62 @@
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr"/>
     </row>
+    <row r="35" ht="40" customHeight="1">
+      <c r="A35" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>№ 458-001.001/002.0/17-26 від 25.09.2026</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>25.09.2026</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>DYSPORT® 500 U (Botulinum toxin type A), ліофілізований порошок, Серія № P08191, P08192, P221368, з маркуванням виробника IPSEN BIOPHARM LTD., -</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36" ht="40" customHeight="1">
+      <c r="A36" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>№ 459-001.001/002.0/17-26 від 25.09.2026</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>25.09.2026</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>TRIPVAC (Diphtheria+tetanus+B-pertussis (DTP), суспензія для ін'єкцій у флаконі, Серія № 221100325A, 221100425A, BIOLOGICAL E. LIMITED,, Індія</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -7063,7 +7063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H63"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8734,17 +8734,17 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>№ 348-001.001/002.0/17-26 від 29.07.2026</t>
+          <t>№ 351-001.001/002.0/17-26 від 31.07.2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>29.07.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>СЕПТАНЕСТ З АДРЕНАЛІНОМ 1/100 000, розчин для ін'єкцій по 1,7 мл у картриджі; по 10 картриджів у блістері; по 5 блістерів у картонній коробці, Серія № L00609BA, СЕПТОДОНТ, Франція</t>
+          <t>ДРОТАВЕРИНУ ГІДРОХЛОРИД, таблетки по 40 мг; по 10 таблеток у блістері; по 2 блістера в пачці з картону, Серія № 40126, АТ "Лубнифарм", Україна</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -8762,17 +8762,17 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>№ 348-001.001/002.0/17-26 від 29.07.2026</t>
+          <t>№ 353-001.001/002.0/17-26 від 31.07.2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>29.07.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>СЕПТАНЕСТ З АДРЕНАЛІНОМ 1/200 000, розчин для ін'єкцій по 1,7 мл у картриджі; по 10 картриджів у блістері; по 5 блістерів у картонній коробці, Серія № L00611AC, СЕПТОДОНТ, Франція</t>
+          <t>всі серії ЛЗ виробництва LIANYUNGANG GUIKE PHARMACEUTICAL CO. LTD., -, Серія № всі серії, LIANYUNGANG GUIKE PHARMACEUTICAL CO. LTD., Китай</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -8783,90 +8783,6 @@
       <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr"/>
       <c r="H60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61" ht="40" customHeight="1">
-      <c r="A61" s="2" t="n">
-        <v>59</v>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>№ 349-001.001/002.0/17-26 від 30.07.2026</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>30.07.2026</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>СЕПТАНЕСТ З АДРЕНАЛІНОМ 1/100 000, розчин для ін'єкцій по 1,7 мл у картриджі; по 10 картриджів у блістері; по 5 блістерів у картонній коробці, Серія № L00609BA, СЕПТОДОНТ, Франція</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>відсутній</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr"/>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62" ht="40" customHeight="1">
-      <c r="A62" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>№ 351-001.001/002.0/17-26 від 31.07.2026</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>31.07.2026</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>ДРОТАВЕРИНУ ГІДРОХЛОРИД, таблетки по 40 мг; по 10 таблеток у блістері; по 2 блістера в пачці з картону, Серія № 40126, АТ "Лубнифарм", Україна</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>відсутній</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr"/>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63" ht="40" customHeight="1">
-      <c r="A63" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>№ 353-001.001/002.0/17-26 від 31.07.2026</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>31.07.2026</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>всі серії ЛЗ виробництва LIANYUNGANG GUIKE PHARMACEUTICAL CO. LTD., -, Серія № всі серії, LIANYUNGANG GUIKE PHARMACEUTICAL CO. LTD., Китай</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>відсутній</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr"/>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11115,7 +11031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -12164,6 +12080,34 @@
       <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr"/>
     </row>
+    <row r="37" ht="40" customHeight="1">
+      <c r="A37" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>№ 461-001.001/002.0/17-26 від 28.09.2026</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>М-М-РВАКСПРО® ВАКЦИНА ДЛЯ ПРОФІЛАКТИКИ КОРУ, ЕПІДЕМІЧНОГО ПАРОТИТУ ТА КРАСНУХИ ЖИВА, порошок для суспензії для ін’єкцій; 1 флакон з порошком (1 доза) та 1 флакон з розчинником (вода для ін’єкцій) по 0,7 мл у картонній коробці; 1 флакон з порошком (1 доза) та 1 попередньо наповнений шприц з розчинником (вода для ін’єкцій) по 0,7 мл в компл, Серія № Z006066, Мерк Шарп і Доум Б.В., Нідерланди, Нідерланди</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -11031,7 +11031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -12030,17 +12030,17 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>№ 458-001.001/002.0/17-26 від 25.09.2026</t>
+          <t>№ 457-001.001/002.0/17-26 від 24.09.2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>25.09.2026</t>
+          <t>24.09.2026</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>DYSPORT® 500 U (Botulinum toxin type A), ліофілізований порошок, Серія № P08191, P08192, P221368, з маркуванням виробника IPSEN BIOPHARM LTD., -</t>
+          <t>ТОБРАДЕКС®, мазь очна, по 3,5 г у тубі; по 1 тубі у коробці з картону, Серія № VDM61B, VFE07A, VLL71A, Алкон-Куврьор, Бельгія</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -12058,7 +12058,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>№ 459-001.001/002.0/17-26 від 25.09.2026</t>
+          <t>№ 458-001.001/002.0/17-26 від 25.09.2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -12068,7 +12068,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>TRIPVAC (Diphtheria+tetanus+B-pertussis (DTP), суспензія для ін'єкцій у флаконі, Серія № 221100325A, 221100425A, BIOLOGICAL E. LIMITED,, Індія</t>
+          <t>DYSPORT® 500 U (Botulinum toxin type A), ліофілізований порошок, Серія № P08191, P08192, P221368, з маркуванням виробника IPSEN BIOPHARM LTD., -</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -12086,17 +12086,17 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>№ 461-001.001/002.0/17-26 від 28.09.2026</t>
+          <t>№ 459-001.001/002.0/17-26 від 25.09.2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>25.09.2026</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>М-М-РВАКСПРО® ВАКЦИНА ДЛЯ ПРОФІЛАКТИКИ КОРУ, ЕПІДЕМІЧНОГО ПАРОТИТУ ТА КРАСНУХИ ЖИВА, порошок для суспензії для ін’єкцій; 1 флакон з порошком (1 доза) та 1 флакон з розчинником (вода для ін’єкцій) по 0,7 мл у картонній коробці; 1 флакон з порошком (1 доза) та 1 попередньо наповнений шприц з розчинником (вода для ін’єкцій) по 0,7 мл в компл, Серія № Z006066, Мерк Шарп і Доум Б.В., Нідерланди, Нідерланди</t>
+          <t>TRIPVAC (Diphtheria+tetanus+B-pertussis (DTP), суспензія для ін'єкцій у флаконі, Серія № 221100325A, 221100425A, BIOLOGICAL E. LIMITED,, Індія</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -12107,6 +12107,34 @@
       <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38" ht="40" customHeight="1">
+      <c r="A38" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>№ 461-001.001/002.0/17-26 від 28.09.2026</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>М-М-РВАКСПРО® ВАКЦИНА ДЛЯ ПРОФІЛАКТИКИ КОРУ, ЕПІДЕМІЧНОГО ПАРОТИТУ ТА КРАСНУХИ ЖИВА, порошок для суспензії для ін’єкцій; 1 флакон з порошком (1 доза) та 1 флакон з розчинником (вода для ін’єкцій) по 0,7 мл у картонній коробці; 1 флакон з порошком (1 доза) та 1 попередньо наповнений шприц з розчинником (вода для ін’єкцій) по 0,7 мл в компл, Серія № Z006066, Мерк Шарп і Доум Б.В., Нідерланди, Нідерланди</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -11031,7 +11031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -12136,6 +12136,146 @@
       <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr"/>
     </row>
+    <row r="39" ht="40" customHeight="1">
+      <c r="A39" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>№ 464-001.001/002.0/17-26 від 29.09.2026</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>COVERSYL NOVUM (Perindopril), таблетки, вкриті плівковою оболонкою, № 90, Серія № A501091, A600041, Les Laboratoires Servier Industrie, Франція</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr"/>
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40" ht="40" customHeight="1">
+      <c r="A40" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>№ 465-001.001/002.0/17-26 від 29.09.2026</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>TRAVNEOS (Avacopan) 10 mg, желатинові капсули, №№ 30, 180, 540, Серія № всі серії, Vifor France, Франція</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr"/>
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41" ht="40" customHeight="1">
+      <c r="A41" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>№ 466-001.001/002.0/17-26 від 29.09.2026</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Choragon® 5000 UI (Human Chorionic Gonadotropin), розчин для ін'єкцій, флакон з ліофілізованим порошком та ампулою розчинника, Серія № всі серії, з маркуванням виробника FERRING GMBH, -</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr"/>
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42" ht="40" customHeight="1">
+      <c r="A42" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>№ 467-001.001/002.0/17-26 від 29.09.2026</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>FLUOROURACIL ACCORD 50 mg/ml (Fluorouracilum), розчин для ін'єкцій або інфузій, у флаконі 20 мл, Серія № P2403768 (bulk: P2403768), H2500329 (bulk: P2403796), G2500676 (bulk: P2404191), Accord Healthcare Polska Sp. z o.o., Польща</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr"/>
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43" ht="40" customHeight="1">
+      <c r="A43" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>№ 468-001.001/002.0/17-26 від 29.09.2026</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>CHORAGON 5000 UI (Human Chorionic Gonadotropin), розчин для ін'єкцій, флакон з ліофілізованим порошком та ампулою розчинника, Серія № k7c01mn, FERRING GMBH, -</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr"/>
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -13,6 +13,7 @@
     <sheet name="Липень 2026" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Серпень 2026" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Вересень 2026" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Жовтень 2026" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -12279,4 +12280,280 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>№ з/п</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Дата і номер розпорядження/ рішення/припису</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Дата одержання розпорядження/ рішення/припису</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Назва лікарських засобів та перелік серій лікарських засобів, зазначених у розпорядженні/ рішенні/приписі</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Результати перевірки щодо наявності зазначених лікарських засобів</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Вжиті заходи у разі виявлення зазначених лікарських засобів</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Дата і номер листа-повідомлення територіальному органу</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Підпис уповноваженої особи</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="40" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="40" customHeight="1">
+      <c r="A3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>№ 479-001.001/002.0/17-26 від 02.10.2026</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>02.10.2026</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>АБІЗОЛ ІЗІТАБ, таблетки, що диспергуються в ротовій порожнині, по 15 мг, по 7 таблеток у блістері, по 4 блістери в картонній упаковці, Серія № EFAP004A, НОБЕЛ ІЛАЧ САНАЇ ВЕ ТІДЖАРЕТ А.Ш., Туреччина</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>№ 480-001.001/002.0/17-26 від 02.10.2026</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>02.10.2026</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Neuralin® (B Complex/Lidocaine/Dexamethasone), розчин, ампула 2 мл  у картонній коробці, Серія № BEG036, PRODUCTOS FARMACEUTICOS, S.A. DE C.V., -</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>№ 480-001.001/002.0/17-26 від 02.10.2026</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>02.10.2026</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>SYNALAR®-C ( Fluocinolon Acetonide/Clioquino) 40g, крем, 40 г у тубі, туба у картонній коробці, Серія № BEH056, PRODUCTOS FARMACEUTICOS, S.A. DE C.V., -</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>№ 480-001.001/002.0/17-26 від 02.10.2026</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>02.10.2026</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>SYNALAR® SIMPLE (Fluocinolon Acetonide), крем, 20 г у тубі, туба у картонній коробці, Серія № BEG060, PRODUCTOS FARMACEUTICOS, S.A. DE C.V., -</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7" ht="40" customHeight="1">
+      <c r="A7" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>№ 480-001.001/002.0/17-26 від 02.10.2026</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>02.10.2026</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>SYNALAR-O® ( Fluocinolone/Polymyxin B/Neomycin/Lidocaine), вушний розчин, 5 мл  у флаконі з піпеткою, флакон у картонній коробці, Серія № BEG001, PRODUCTOS FARMACEUTICOS, S.A. DE C.V., -</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8" ht="40" customHeight="1">
+      <c r="A8" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>№ 480-001.001/002.0/17-26 від 02.10.2026</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>02.10.2026</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>ALIN® DEPOT (Dexamethasone), розчин 2 мл  у попередньо заповненому шприці, у картонній коробці, Серія № BEF056, PRODUCTOS FARMACEUTICOS, S.A. DE C.V., -</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -7064,7 +7064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:H59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8707,17 +8707,17 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>№ 346-001.001/002.0/17-26 від 29.07.2026</t>
+          <t>№ 351-001.001/002.0/17-26 від 31.07.2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>29.07.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>ЦИТРАМОН В, таблетки;  по  10 таблеток у блістерах, Серія № 61025, ПАТ "Монфарм", Україна</t>
+          <t>ДРОТАВЕРИНУ ГІДРОХЛОРИД, таблетки по 40 мг; по 10 таблеток у блістері; по 2 блістера в пачці з картону, Серія № 40126, АТ "Лубнифарм", Україна</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -8735,7 +8735,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>№ 351-001.001/002.0/17-26 від 31.07.2026</t>
+          <t>№ 353-001.001/002.0/17-26 від 31.07.2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -8745,7 +8745,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>ДРОТАВЕРИНУ ГІДРОХЛОРИД, таблетки по 40 мг; по 10 таблеток у блістері; по 2 блістера в пачці з картону, Серія № 40126, АТ "Лубнифарм", Україна</t>
+          <t>всі серії ЛЗ виробництва LIANYUNGANG GUIKE PHARMACEUTICAL CO. LTD., -, Серія № всі серії, LIANYUNGANG GUIKE PHARMACEUTICAL CO. LTD., Китай</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -8756,34 +8756,6 @@
       <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr"/>
       <c r="H59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60" ht="40" customHeight="1">
-      <c r="A60" s="2" t="n">
-        <v>58</v>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>№ 353-001.001/002.0/17-26 від 31.07.2026</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>31.07.2026</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>всі серії ЛЗ виробництва LIANYUNGANG GUIKE PHARMACEUTICAL CO. LTD., -, Серія № всі серії, LIANYUNGANG GUIKE PHARMACEUTICAL CO. LTD., Китай</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>відсутній</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr"/>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12288,7 +12260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -12553,6 +12525,90 @@
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr"/>
     </row>
+    <row r="9" ht="40" customHeight="1">
+      <c r="A9" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>№ 483-001.2/002.0/17-26 від 06.10.2026</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>06.10.2026</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>МЕФЕНАМІНОВА КИСЛОТА, таблетки по 500 мг, по 10 таблеток у блістері, по 2 блістери в пачці, Серія № 070425, ТОВ "Фармацевтична компанія "ФарКоС", Україна</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>№ 484-001.2/002.0/17-26 від 06.10.2026</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>06.10.2026</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>МЕФЕНАМІНОВА КИСЛОТА, таблетки по 500 мг, по 10 таблеток у блістері, по 2 блістери в пачці, Серія № 100925, ТОВ "Фармацевтична компанія "ФарКоС", Україна</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>№ 485-001.2/002.0/17-26 від 06.10.2026</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>06.10.2026</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>QDENGA® (Tetravalent live attenuated virus vaccine against dengue), розчин, флакон у коробці, Серія № всі серії, TAKEDA GMBH, -</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -12260,7 +12260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -12609,6 +12609,34 @@
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr"/>
     </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>№ 487-001.2/002.0/17-26 від 06.10.2026</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>06.10.2026</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>НІМЕСУЛІД, порошок (субстанція) у подвійних пакетах з поліетилену для фармацевтичного застосування, Серія № NMS/125010052, Аарті Драгз Лімітед, Індія</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -12260,7 +12260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -12637,6 +12637,34 @@
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr"/>
     </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>№ 488-001.2/002.0/17-26 від 07.10.2026</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>07.10.2026</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>всі ЛЗ,  виробництва Glukem Biocare Private Limited, -, Серія № всі серії, Glukem Biocare Private Limited, Індія</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -12260,7 +12260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -12665,6 +12665,34 @@
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr"/>
     </row>
+    <row r="14" ht="40" customHeight="1">
+      <c r="A14" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>№ Проект від 08.10.2026</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>08.10.2026</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>TRODELVY (Sacituzumab govitecan) 200 mg, порошок для концентрату розчину для інфузій, Серія № S211004D, Gilead  Sciences Ilac Tic.Ltd. Sti, Ірландія</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -12260,7 +12260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -12671,7 +12671,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>№ Проект від 08.10.2026</t>
+          <t>№ 489-001.2/002.0/17-26 від 08.10.2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>TRODELVY (Sacituzumab govitecan) 200 mg, порошок для концентрату розчину для інфузій, Серія № S211004D, Gilead  Sciences Ilac Tic.Ltd. Sti, Ірландія</t>
+          <t>BACTERIOSTATIC WATER, вода для ін’єкцій у  скляному флаконі, Серія № всі серії, з маркуванням MAGNUS PHARMACEUTICALS, -</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -12692,6 +12692,34 @@
       <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15" ht="40" customHeight="1">
+      <c r="A15" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>№ Проект від 08.10.2026</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>08.10.2026</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>TRODELVY (Sacituzumab govitecan) 200 mg, порошок для концентрату розчину для інфузій, Серія № S211004D, Gilead  Sciences Ilac Tic.Ltd. Sti, Ірландія</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -12260,7 +12260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -12721,6 +12721,118 @@
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr"/>
     </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>№ 490-001.2/002.0/17-26 від 09.10.2026</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>09.10.2026</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>METHYLDOPA REMEDICA  250mg (Methyldopa), таблетки  в блістері , блістери в картонній упаковці №30,№100, Серія № 113216, 115732, Remedica Ltd., CYPRUS</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17" ht="40" customHeight="1">
+      <c r="A17" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>№ 491-001.2/002.0/17-26 від 09.10.2026</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>09.10.2026</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>TRODELVY (Sacituzumab govitecan) 200 mg, порошок для концентрату розчину для інфузій, Серія № S211004D, Gilead  Sciences Ilac Tic.Ltd. Sti, Ірландія</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18" ht="40" customHeight="1">
+      <c r="A18" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>№ 492-001.2/002.0/17-26 від 09.10.2026</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>09.10.2026</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>TEST P TESTOSTERONE PROPIONATE,( Testosterone Propionate 100mg), розчин для ін'єкцій  у скляному флаконі темного кольору , флакон у картонній коробці, 10 мл у флаконі, MP MAGNUS PHARMACEUTICALS, Індія</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19" ht="40" customHeight="1">
+      <c r="A19" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>№ Проект від 09.10.2026</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>09.10.2026</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>PHESGO (PERTUZUMABE + TRASTUZUMABE / PERTUZUMAB + TRASTUZUMAB), 600 mg + 600 mg, Парентеральний  розчин малого об’єму, Серія № B5011B05, F. HOFFMANN - LA ROCHE LTD, Бразилія</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -12260,7 +12260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -12833,6 +12833,34 @@
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr"/>
     </row>
+    <row r="20" ht="40" customHeight="1">
+      <c r="A20" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>№ Проект від 09.10.2026</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>09.10.2026</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>PHESGO ( PERTUZUMAB + TRASTUZUMAB), 600 mg + 600 mg, аспептично оброблений розчин для парентерального введення малого об’єму, Серія № B5011B05, F. HOFFMANN - LA ROCHE LTD, Бразилія</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -12260,7 +12260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -12811,7 +12811,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>№ Проект від 09.10.2026</t>
+          <t>№ 492-001.2/002.0/17-26 від 09.10.2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -12821,7 +12821,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>PHESGO (PERTUZUMABE + TRASTUZUMABE / PERTUZUMAB + TRASTUZUMAB), 600 mg + 600 mg, Парентеральний  розчин малого об’єму, Серія № B5011B05, F. HOFFMANN - LA ROCHE LTD, Бразилія</t>
+          <t>TEST P TESTOSTERONE PROPIONATE,( Testosterone Propionate 100mg), розчин для ін'єкцій  у скляному флаконі темного кольору, флакон у картонній коробці, 10 мл у флаконі, Серія № всі серії, MAGNUS PHARMACEUTICALS, Індія</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -12849,7 +12849,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>PHESGO ( PERTUZUMAB + TRASTUZUMAB), 600 mg + 600 mg, аспептично оброблений розчин для парентерального введення малого об’єму, Серія № B5011B05, F. HOFFMANN - LA ROCHE LTD, Бразилія</t>
+          <t>PHESGO (PERTUZUMABE + TRASTUZUMABE / PERTUZUMAB + TRASTUZUMAB), 600 mg + 600 mg, Парентеральний  розчин малого об’єму, Серія № B5011B05, F. HOFFMANN - LA ROCHE LTD, Бразилія</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -12860,6 +12860,62 @@
       <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21" ht="40" customHeight="1">
+      <c r="A21" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>№ Проект від 09.10.2026</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>09.10.2026</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>PHESGO ( PERTUZUMAB + TRASTUZUMAB), 600 mg + 600 mg, аспептично оброблений розчин для парентерального введення малого об’єму, Серія № B5011B05, F. HOFFMANN - LA ROCHE LTD, Бразилія</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>№ Проект від 12.10.2026</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>12.10.2026</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>ENHERTU 100 mg (trastuzumab deruxtecan), Ліофілізований порошок, Серія № 432221, 432844, 432862, DAIICHI SANKYO EUROPE GMBH, -</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -12260,7 +12260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -12917,6 +12917,118 @@
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr"/>
     </row>
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>№ 498-001.1.01/002.0/17-26 від 13.10.2026</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>13.10.2026</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>PHESGO ( PERTUZUMAB + TRASTUZUMAB), 600 mg + 600 mg, аспептично оброблений розчин для парентерального введення малого об’єму, Серія № B5011B05, F. HOFFMANN - LA ROCHE LTD, Бразилія</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>№ 499-001.1.01/002.0/17-26 від 13.10.2026</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>13.10.2026</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>ENHERTU 100 mg (trastuzumab deruxtecan), Ліофілізований порошок, Серія № 432221, 432844, 432862, DAIICHI SANKYO EUROPE GMBH, -</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>№ 500-001.1.01/002.0/17-26 від 13.10.2026</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>13.10.2026</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>DYSPORT 500 U (Botulinum toxin type A), порошок для розчину для ін'єкцій, по 500 ОД, Серія № 031525, Ipsen Biopharm Ltd, -</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26" ht="40" customHeight="1">
+      <c r="A26" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>№ 501-001.1.01/002.0/17-26 від 13.10.2026</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>13.10.2026</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>KEYTRUDA (Pembrolizumab) 25 mg/ml, 100 мл у флаконі, Серія № Z004514, Z006129, Z006709, Z007908, Z008568, Z013426, Z015652, Z015833, Z007415, Z016478, Merck Sharp &amp; Dohme B.V., -</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -12260,7 +12260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -13029,6 +13029,230 @@
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr"/>
     </row>
+    <row r="27" ht="40" customHeight="1">
+      <c r="A27" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>№ 502-001.1.01/002.0/17-26 від 16.10.2026</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>16.10.2026</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>MEROPENEM (Meropenem) 1ml, розчин для ін’єкцій, у флаконі, флакон у картонній коробці, Серія № X2MF160A, з маркуванням виробника VENUS REMEDIES LIMITED., -</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28" ht="40" customHeight="1">
+      <c r="A28" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>№ 503-001.1.01/002.0/17-26 від 16.10.2026</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>16.10.2026</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>APOZEMIA XR (Metformin ) 500 mg LP, таблетки у блістері, блістер у коробці, 60 таблеток, Серія № 1108G24A, PROTEIN, S. A. DE C. V, -</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29" ht="40" customHeight="1">
+      <c r="A29" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>№ 504-001.1.01/002.0/17-26 від 16.10.2026</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>16.10.2026</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>DAPAGLIFLOZINA (Dapagliflozin), таблетки у великій упаковці, Серія № AF3183, AF3187, AF3200, AF3206, AsztraZeneca, S. A. de C.V., -</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30" ht="40" customHeight="1">
+      <c r="A30" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>№ 505-001.1.01/002.0/17-26 від 16.10.2026</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>16.10.2026</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>CLORIDRATO DE DOBUTAMINE ( dobutamine hydrochloride) 12,5 мг/мл, Термінально стерильний парентеральний розчин малого об'єму, флакон 20 мл, флакон в упаковці., Серія № 24092127, 24102310, 25102244, 25102243, 25112308., HYPOFARMA - INSTITUTO DE HYPODERMIA E FARMACIA LTDA, -</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31" ht="40" customHeight="1">
+      <c r="A31" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>№ 506-001.1.01/002.0/17-26 від 16.10.2026</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>16.10.2026</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>AGIN® (acetylsalicylic acid/ascorbic acid/sulfadiazine.), 300/250/300 mg, таблетки  у блістері , блістери в коробці  №60, Серія № 7825, Quimica Franco Mexicana Nordin, S.A. de C.V., -</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32" ht="40" customHeight="1">
+      <c r="A32" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>№ 507-001.1.01/002.0/17-26 від 16.10.2026</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>16.10.2026</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>BUSCAPINA®COMPOSITUM (Hioscine/Metamizole sodium) 10 mg/250, таблетки у блістері, блістер у картонній коробці № 36, Серія № CMXA007, C57411, з маркуванням виробника Boehringer Ingelheim Promeco, S.A. de C.V., -</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33" ht="40" customHeight="1">
+      <c r="A33" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>№ 507-001.1.01/002.0/17-26 від 16.10.2026</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>16.10.2026</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>BUSCAPINA®COMPOSITUM (Hioscine/Metamizole sodium) 10 mg/250, таблетки у блістері, блістер у картонній коробці № 24, Серія № CMXA001, з маркуванням виробника Boehringer Ingelheim Promeco, S.A. de C.V., -</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34" ht="40" customHeight="1">
+      <c r="A34" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>№ 508-001.1.01/002.0/17-26 від 16.10.2026</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>16.10.2026</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>СРІБЛО КОЛОЇДНЕ, пластинки або порошок (субстанція) у поліетиленових мішках або поліетиленових пляшках для фармацевтичного застосування, Серія № С26-0136, ЛАБОРАТОРІОС АРГЕНОЛ С.Л., Іспанія</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -12260,7 +12260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -13253,6 +13253,34 @@
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr"/>
     </row>
+    <row r="35" ht="40" customHeight="1">
+      <c r="A35" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>№ 509-001.1/002.1/17-26 від 19.10.2026</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>19.10.2026</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>ORNISPAR (Ornithinі aspartas), 3 g/5 g, гранули для перорального розчину, в саше, Серія № 02102554, 03102554, 04102554, Medicofarma S.A., Poland</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -12260,7 +12260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -13281,6 +13281,286 @@
       <c r="G35" s="2" t="inlineStr"/>
       <c r="H35" s="2" t="inlineStr"/>
     </row>
+    <row r="36" ht="40" customHeight="1">
+      <c r="A36" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>№ 510-001.1/002.1/17-26 від 20.10.2026</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>20.10.2026</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>ДРОТАВЕРИНУ ГІДРОХЛОРИД, таблетки по 40 мг, по 10 таблеток у блістері; по 2 блістери в пачці з картону, Серія № 170226, ПАТ "Лубнифарм", Україна</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37" ht="40" customHeight="1">
+      <c r="A37" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>№ 511-001.1/002.1/17-26 від 20.10.2026</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>20.10.2026</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>SORTEC (Sorafenib), 200 mg, таблетки у флаконі, флакон у картонній коробці №112, Серія № 5CE003A, Ulsa Tech, S. A. DE C. V., -</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38" ht="40" customHeight="1">
+      <c r="A38" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>№ 512-001.1/002.1/17-26 від 20.10.2026</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>20.10.2026</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>PDP-DIPHENHYDRAMINE  (Chlorhydrate de diphenhydramine )25 mg25mg 100 CAPS, капсули у флаконі № 100, Серія № 642913, 643904, 648034, 651074, 653544, 656693, Pharmascience Inc., Канада</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39" ht="40" customHeight="1">
+      <c r="A39" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>№ 513-001.1/002.1/17-26 від 20.10.2026</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>20.10.2026</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>CIPLAVASC 5 ( Amlodipine besylate), 5mg, таблетки в картонній коробці №30, Серія № ZA260565, Cipla Medpro (Pty) Ltd, Південно-Африканська Республіка</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr"/>
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40" ht="40" customHeight="1">
+      <c r="A40" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>№ 514-001.1/002.1/17-26 від 20.10.2026</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>20.10.2026</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>BEDOYECTA® (B Complex, Folic Acid, Vitamin C, and Rutin), (36 mg/5 mg/10 mg/0.018 mg), 0.5 mg, 100 mg, 5mg., капсули в коробці № 30, Серія № 230593, 230589, Catalent Argentina SAIC, -</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr"/>
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41" ht="40" customHeight="1">
+      <c r="A41" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>№ 515-001.1/002.1/17-26 від 20.10.2026</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>20.10.2026</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>pms-FAMPRIDINE (Fampridine), 10mg, таблетки у флаконі № 60, Серія № 24123884, ALKEM LABORATORIES LTD., Індія</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr"/>
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42" ht="40" customHeight="1">
+      <c r="A42" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>№ 516-001.1/002.1/17-26 від 20.10.2026</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>20.10.2026</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>TIRZEPATIDE 20 mg/1,5 ml, стерильна одноразова ручка з попередньо заповненим картриджем у кратонній коробці, Серія № всі серії, з маркуванням виробника Polypeptide-group Pharmaceutical Co., Ltd., Sweden</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr"/>
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43" ht="40" customHeight="1">
+      <c r="A43" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>№ 517-001.1/002.1/17-26 від 20.10.2026</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>20.10.2026</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>SYDOLIL® (Acetylsalicylic acid/Caffeine/Ergotamine),400/50/1 mg, таблетки в коробці №12, Серія № 102910, SIEGFRIED RHEIN, S. A. DE C. V., -</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr"/>
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44" ht="40" customHeight="1">
+      <c r="A44" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>№ 518-001.1/002.1/17-26 від 20.10.2026</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>20.10.2026</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>NEO-MELUBRINA® (Metamizole sodium), 500 mg., таблетки в коробці №10, Серія № FMX0999, SANOFI-AVENTIS DE MEXICO, S.A. DE C.V, Мексика</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr"/>
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45" ht="40" customHeight="1">
+      <c r="A45" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>№ 519-001.1/002.1/17-26 від 20.10.2026</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>20.10.2026</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>SINUBERASE® (Bacillus clausii spore),4 billions UFC., пероральна суспензія в ампулах,  ампули в коробці № 20, Серія № 5I132, LABORATOIRE UNITHER, -</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr"/>
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -12260,7 +12260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -13561,6 +13561,202 @@
       <c r="G45" s="2" t="inlineStr"/>
       <c r="H45" s="2" t="inlineStr"/>
     </row>
+    <row r="46" ht="40" customHeight="1">
+      <c r="A46" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>№ 520-001.1/002.1/17-26 від 22.10.2026</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>22.10.2026</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>ГРИПОМЕД®, капсули, по 10 капсул у блістері; по 2 блістери у пачці з картону, Серія № 070925, ПАТ "Хімфармзавод "Червона зірка", Україна</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr"/>
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47" ht="40" customHeight="1">
+      <c r="A47" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>№ 521-001.1/002.1/17-26 від 22.10.2026</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>22.10.2026</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>ПЕРЕКИС - ВІШФА, розчин для зовнішнього застосування 3 %; по 100 мл у флаконах полімерних, Серія № 60825, ТОВ "ДКП "Фармацевтична фабрика", Україна</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr"/>
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48" ht="40" customHeight="1">
+      <c r="A48" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>№ 522-001.1/002.1/17-26 від 22.10.2026</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>22.10.2026</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>АБРОЛ®, таблетки по 30 мг; по 10 таблеток у блістері; по 2 блістери в упаковці, Серія № SAA5001, ТОВ "КУСУМ ФАРМ", Україна</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr"/>
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49" ht="40" customHeight="1">
+      <c r="A49" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>№ 524-001.1/002.1/17-26 від 22.10.2026</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>22.10.2026</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>ЕМЛА, крем по 30 г у тубі; по 1 тубі у картонній коробці, Серія № 100272, Ресіфарм Карлскога АБ, Швеція</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr"/>
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50" ht="40" customHeight="1">
+      <c r="A50" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>№ 525-001.1/002.1/17-26 від 22.10.2026</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>22.10.2026</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>LIZBI (LINEZOLID),  2ml, термінально стерилізовані парентеральні розчини великих об'ємів, Серія № 0000207107, HALEX ІSTAR INDUSTRIA FARMACEUTICA S.A., Бразилія</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr"/>
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51" ht="40" customHeight="1">
+      <c r="A51" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>№ 526-001.1/002.1/17-26 від 22.10.2026</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>22.10.2026</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>ADEROGYL® (Vitamin C, Vitamin D2, Vitamin A), 163.697 mg/400 UI/2000 UІ, скляна ампула з оральним розчином, ампули в коробці №5, Серія № CMXA037, Sanofi-Aventis de Mexico, S.A. de C.V., Мексика</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr"/>
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52" ht="40" customHeight="1">
+      <c r="A52" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>№ 527-001.1/002.1/17-26 від 22.10.2026</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>22.10.2026</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>IMAAVY (Nipocalimab), 300mg, Аспептично оброблені парентеральні розчини малого об’єму, Серія № JNYJ1201, VETTER PHARMA-FERTIGUNG GMBH &amp; CO. KG., Німеччина</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr"/>
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -12260,7 +12260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -13399,7 +13399,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>№ 514-001.1/002.1/17-26 від 20.10.2026</t>
+          <t>№ 513-001.1/002.1/17-26 від 20.10.2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -13409,7 +13409,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>BEDOYECTA® (B Complex, Folic Acid, Vitamin C, and Rutin), (36 mg/5 mg/10 mg/0.018 mg), 0.5 mg, 100 mg, 5mg., капсули в коробці № 30, Серія № 230593, 230589, Catalent Argentina SAIC, -</t>
+          <t>CIPLAVASC 5 ( Amlodipine besylate), 5mg, таблетки в картонній коробці №30, Серія № ZA260565, Cipla Medpro (Pty) Ltd., Південно-Африканська Республіка</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -13427,7 +13427,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>№ 515-001.1/002.1/17-26 від 20.10.2026</t>
+          <t>№ 514-001.1/002.1/17-26 від 20.10.2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -13437,7 +13437,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>pms-FAMPRIDINE (Fampridine), 10mg, таблетки у флаконі № 60, Серія № 24123884, ALKEM LABORATORIES LTD., Індія</t>
+          <t>BEDOYECTA® (B Complex, Folic Acid, Vitamin C, and Rutin), (36 mg/5 mg/10 mg/0.018 mg), 0.5 mg, 100 mg, 5mg., капсули в коробці № 30, Серія № 230593, 230589, Catalent Argentina SAIC, -</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -13455,7 +13455,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>№ 516-001.1/002.1/17-26 від 20.10.2026</t>
+          <t>№ 515-001.1/002.1/17-26 від 20.10.2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -13465,7 +13465,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>TIRZEPATIDE 20 mg/1,5 ml, стерильна одноразова ручка з попередньо заповненим картриджем у кратонній коробці, Серія № всі серії, з маркуванням виробника Polypeptide-group Pharmaceutical Co., Ltd., Sweden</t>
+          <t>pms-FAMPRIDINE (Fampridine), 10mg, таблетки у флаконі № 60, Серія № 24123884, ALKEM LABORATORIES LTD., Індія</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -13483,7 +13483,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>№ 517-001.1/002.1/17-26 від 20.10.2026</t>
+          <t>№ 516-001.1/002.1/17-26 від 20.10.2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -13493,7 +13493,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>SYDOLIL® (Acetylsalicylic acid/Caffeine/Ergotamine),400/50/1 mg, таблетки в коробці №12, Серія № 102910, SIEGFRIED RHEIN, S. A. DE C. V., -</t>
+          <t>TIRZEPATIDE 20 mg/1,5 ml, стерильна одноразова ручка з попередньо заповненим картриджем у кратонній коробці, Серія № всі серії, з маркуванням виробника Polypeptide-group Pharmaceutical Co., Ltd., Sweden</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -13511,7 +13511,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>№ 518-001.1/002.1/17-26 від 20.10.2026</t>
+          <t>№ 517-001.1/002.1/17-26 від 20.10.2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -13521,7 +13521,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>NEO-MELUBRINA® (Metamizole sodium), 500 mg., таблетки в коробці №10, Серія № FMX0999, SANOFI-AVENTIS DE MEXICO, S.A. DE C.V, Мексика</t>
+          <t>SYDOLIL® (Acetylsalicylic acid/Caffeine/Ergotamine),400/50/1 mg, таблетки в коробці №12, Серія № 102910, SIEGFRIED RHEIN, S. A. DE C. V., -</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -13539,7 +13539,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>№ 519-001.1/002.1/17-26 від 20.10.2026</t>
+          <t>№ 518-001.1/002.1/17-26 від 20.10.2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -13549,7 +13549,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>SINUBERASE® (Bacillus clausii spore),4 billions UFC., пероральна суспензія в ампулах,  ампули в коробці № 20, Серія № 5I132, LABORATOIRE UNITHER, -</t>
+          <t>NEO-MELUBRINA® (Metamizole sodium), 500 mg., таблетки в коробці №10, Серія № FMX0999, SANOFI-AVENTIS DE MEXICO, S.A. DE C.V, Мексика</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -13567,17 +13567,17 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>№ 520-001.1/002.1/17-26 від 22.10.2026</t>
+          <t>№ 518-001.1/002.1/17-26 від 20.10.2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>22.10.2026</t>
+          <t>20.10.2026</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>ГРИПОМЕД®, капсули, по 10 капсул у блістері; по 2 блістери у пачці з картону, Серія № 070925, ПАТ "Хімфармзавод "Червона зірка", Україна</t>
+          <t>NEO-MELUBRINA® (Metamizole sodium), 500 mg., таблетки в коробці №10, Серія № FMX0999, SANOFI-AVENTIS DE MEXICO, S.A. DE C.V., Мексика</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -13595,17 +13595,17 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>№ 521-001.1/002.1/17-26 від 22.10.2026</t>
+          <t>№ 519-001.1/002.1/17-26 від 20.10.2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>22.10.2026</t>
+          <t>20.10.2026</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>ПЕРЕКИС - ВІШФА, розчин для зовнішнього застосування 3 %; по 100 мл у флаконах полімерних, Серія № 60825, ТОВ "ДКП "Фармацевтична фабрика", Україна</t>
+          <t>SINUBERASE® (Bacillus clausii spore),4 billions UFC., пероральна суспензія в ампулах,  ампули в коробці № 20, Серія № 5I132, LABORATOIRE UNITHER, -</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -13623,7 +13623,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>№ 522-001.1/002.1/17-26 від 22.10.2026</t>
+          <t>№ 520-001.1/002.1/17-26 від 22.10.2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -13633,7 +13633,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>АБРОЛ®, таблетки по 30 мг; по 10 таблеток у блістері; по 2 блістери в упаковці, Серія № SAA5001, ТОВ "КУСУМ ФАРМ", Україна</t>
+          <t>ГРИПОМЕД®, капсули, по 10 капсул у блістері; по 2 блістери у пачці з картону, Серія № 070925, ПАТ "Хімфармзавод "Червона зірка", Україна</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -13651,7 +13651,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>№ 524-001.1/002.1/17-26 від 22.10.2026</t>
+          <t>№ 521-001.1/002.1/17-26 від 22.10.2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -13661,7 +13661,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>ЕМЛА, крем по 30 г у тубі; по 1 тубі у картонній коробці, Серія № 100272, Ресіфарм Карлскога АБ, Швеція</t>
+          <t>ПЕРЕКИС - ВІШФА, розчин для зовнішнього застосування 3 %; по 100 мл у флаконах полімерних, Серія № 60825, ТОВ "ДКП "Фармацевтична фабрика", Україна</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -13679,7 +13679,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>№ 525-001.1/002.1/17-26 від 22.10.2026</t>
+          <t>№ 522-001.1/002.1/17-26 від 22.10.2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -13689,7 +13689,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>LIZBI (LINEZOLID),  2ml, термінально стерилізовані парентеральні розчини великих об'ємів, Серія № 0000207107, HALEX ІSTAR INDUSTRIA FARMACEUTICA S.A., Бразилія</t>
+          <t>АБРОЛ®, таблетки по 30 мг; по 10 таблеток у блістері; по 2 блістери в упаковці, Серія № SAA5001, ТОВ "КУСУМ ФАРМ", Україна</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -13707,7 +13707,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>№ 526-001.1/002.1/17-26 від 22.10.2026</t>
+          <t>№ 524-001.1/002.1/17-26 від 22.10.2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -13717,7 +13717,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>ADEROGYL® (Vitamin C, Vitamin D2, Vitamin A), 163.697 mg/400 UI/2000 UІ, скляна ампула з оральним розчином, ампули в коробці №5, Серія № CMXA037, Sanofi-Aventis de Mexico, S.A. de C.V., Мексика</t>
+          <t>ЕМЛА, крем по 30 г у тубі; по 1 тубі у картонній коробці, Серія № 100272, Ресіфарм Карлскога АБ, Швеція</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -13735,7 +13735,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>№ 527-001.1/002.1/17-26 від 22.10.2026</t>
+          <t>№ 525-001.1/002.1/17-26 від 22.10.2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -13745,7 +13745,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>IMAAVY (Nipocalimab), 300mg, Аспептично оброблені парентеральні розчини малого об’єму, Серія № JNYJ1201, VETTER PHARMA-FERTIGUNG GMBH &amp; CO. KG., Німеччина</t>
+          <t>LIZBI (LINEZOLID),  2ml, термінально стерилізовані парентеральні розчини великих об'ємів, Серія № 0000207107, HALEX ІSTAR INDUSTRIA FARMACEUTICA S.A., Бразилія</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -13756,6 +13756,62 @@
       <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53" ht="40" customHeight="1">
+      <c r="A53" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>№ 526-001.1/002.1/17-26 від 22.10.2026</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>22.10.2026</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>ADEROGYL® (Vitamin C, Vitamin D2, Vitamin A), 163.697 mg/400 UI/2000 UІ, скляна ампула з оральним розчином, ампули в коробці №5, Серія № CMXA037, Sanofi-Aventis de Mexico, S.A. de C.V., Мексика</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr"/>
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54" ht="40" customHeight="1">
+      <c r="A54" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>№ 527-001.1/002.1/17-26 від 22.10.2026</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>22.10.2026</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>IMAAVY (Nipocalimab), 300mg, Аспептично оброблені парентеральні розчини малого об’єму, Серія № JNYJ1201, VETTER PHARMA-FERTIGUNG GMBH &amp; CO. KG., Німеччина</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr"/>
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -7064,7 +7064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8371,7 +8371,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>№ 337-001.001/002.0/17-26 від 27.07.2026</t>
+          <t>№ 338-001.001/002.0/17-26 від 27.07.2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -8381,7 +8381,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>ЛОПЕРАМІД, таблетки по 2 мг по 10 таблеток у блістері; по 2 блістери в пачці, Серія № 011188, ТОВ "МАРІФАРМ", Словенія</t>
+          <t>ГРИПОМЕД®, капсули, по 10 капсул у блістері; по 2 блістери у пачці з картону, Серія № 070925, ПАТ "Хімфармзавод "Червона зірка", Україна</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -8399,7 +8399,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>№ 338-001.001/002.0/17-26 від 27.07.2026</t>
+          <t>№ 342-001.001/002.0/17-26 від 27.07.2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -8409,7 +8409,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>ГРИПОМЕД®, капсули, по 10 капсул у блістері; по 2 блістери у пачці з картону, Серія № 070925, ПАТ "Хімфармзавод "Червона зірка", Україна</t>
+          <t>САЛІЦИЛОВА МАЗЬ, мазь 10 % по 25 г у тубі ламінатній в пачці, Серія № 010124, ПрАТ Фармацевтична фабрика "Віола", Україна</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -8427,7 +8427,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>№ 339-001.001/002.0/17-26 від 27.07.2026</t>
+          <t>№ 342-001.001/002.0/17-26 від 27.07.2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -8437,7 +8437,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>ГАБАНА®, капсули по 300 мг, по 10 капсул у блістері; по 2 блістери в пачці, Серія № 011523, ТОВ «МАРІФАРМ», Словенія</t>
+          <t>САЛІЦИЛОВА МАЗЬ, мазь 10% по 25 г у тубі ламінатній в пачці, Серія № 090824, ПрАТ Фармацевтична фабрика "Віола", Україна</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -8455,7 +8455,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>№ 339-001.001/002.0/17-26 від 27.07.2026</t>
+          <t>№ 342-001.001/002.0/17-26 від 27.07.2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -8465,7 +8465,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>ГАБАНА®, капсули по 300 мг, по 10 капсул у блістері; по 2 блістери в пачці, Серія № 011520, ТОВ «МАРІФАРМ», Словенія</t>
+          <t>САЛІЦИЛОВА МАЗЬ, мазь 10 % по 25 г у тубі ламінатній; по 1 тубі в пачці, Серія № 111023, ПрАТ Фармацевтична фабрика "Віола", Україна</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -8483,17 +8483,17 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>№ 339-001.001/002.0/17-26 від 27.07.2026</t>
+          <t>№ 343-001.001/002.0/17-26 від 28.07.2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>28.07.2026</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>ГАБАНА®, капсули по 300 мг, по 10 капсул у блістері; по 2 блістери в пачці, Серія № 011502, ТОВ «МАРІФАРМ», Словенія</t>
+          <t>ЕМЛА, крем по 30 г у тубі; по 1 тубі у картонній коробці, Серія № 100272, Ресіфарм Карлскога АБ, Австрія</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -8511,17 +8511,17 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>№ 342-001.001/002.0/17-26 від 27.07.2026</t>
+          <t>№ 344-001.001/002.0/17-26 від 28.07.2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>28.07.2026</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>САЛІЦИЛОВА МАЗЬ, мазь 10 % по 25 г у тубі ламінатній в пачці, Серія № 010124, ПрАТ Фармацевтична фабрика "Віола", Україна</t>
+          <t>VALAMOR (ribociclib) 200 mg, таблетки № 63, Серія № A0213K, Novartis Sagl?k, G?da ve Tar?m Urunleri San. ve Tic. A.S., -</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -8539,17 +8539,17 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>№ 342-001.001/002.0/17-26 від 27.07.2026</t>
+          <t>№ 345-001.001/002.0/17-26 від 28.07.2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>28.07.2026</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>САЛІЦИЛОВА МАЗЬ, мазь 10% по 25 г у тубі ламінатній в пачці, Серія № 090824, ПрАТ Фармацевтична фабрика "Віола", Україна</t>
+          <t>ФІБРИНАЗА-20, таблетки, вкриті оболонкою, кишковорозчинні по 20 мг; по 10 таблеток у блістері; по 3 блістери у картонній пачці, Серія № EBK25010B1, EBK25011B1, EBK25012B1, EBK26004B1, EBK26005B1, EBK26007B1, Евертоджен Лайф Саєнсиз  Лімітед, Індія</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -8567,17 +8567,17 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>№ 342-001.001/002.0/17-26 від 27.07.2026</t>
+          <t>№ 345-001.001/002.0/17-26 від 28.07.2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>28.07.2026</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>САЛІЦИЛОВА МАЗЬ, мазь 10 % по 25 г у тубі ламінатній; по 1 тубі в пачці, Серія № 111023, ПрАТ Фармацевтична фабрика "Віола", Україна</t>
+          <t>ФІБРИНАЗА-10, таблетки, вкриті оболонкою, кишковорозчинні по 10 мг, по 10 таблеток у блістері; по 3 блістери у картонній пачці, Серія № ESI25011B1, ESI25012B1, ESI26002B1, ESI26003B1, Евертоджен Лайф Саєнсиз Лімітед, Індія</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -8595,17 +8595,17 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>№ 343-001.001/002.0/17-26 від 28.07.2026</t>
+          <t>№ 351-001.001/002.0/17-26 від 31.07.2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>28.07.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>ЕМЛА, крем по 30 г у тубі; по 1 тубі у картонній коробці, Серія № 100272, Ресіфарм Карлскога АБ, Австрія</t>
+          <t>ДРОТАВЕРИНУ ГІДРОХЛОРИД, таблетки по 40 мг; по 10 таблеток у блістері; по 2 блістера в пачці з картону, Серія № 40126, АТ "Лубнифарм", Україна</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -8623,17 +8623,17 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>№ 344-001.001/002.0/17-26 від 28.07.2026</t>
+          <t>№ 353-001.001/002.0/17-26 від 31.07.2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>28.07.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>VALAMOR (ribociclib) 200 mg, таблетки № 63, Серія № A0213K, Novartis Sagl?k, G?da ve Tar?m Urunleri San. ve Tic. A.S., -</t>
+          <t>всі серії ЛЗ виробництва LIANYUNGANG GUIKE PHARMACEUTICAL CO. LTD., -, Серія № всі серії, LIANYUNGANG GUIKE PHARMACEUTICAL CO. LTD., Китай</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -8644,118 +8644,6 @@
       <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr"/>
       <c r="H55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56" ht="40" customHeight="1">
-      <c r="A56" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>№ 345-001.001/002.0/17-26 від 28.07.2026</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>28.07.2026</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>ФІБРИНАЗА-20, таблетки, вкриті оболонкою, кишковорозчинні по 20 мг; по 10 таблеток у блістері; по 3 блістери у картонній пачці, Серія № EBK25010B1, EBK25011B1, EBK25012B1, EBK26004B1, EBK26005B1, EBK26007B1, Евертоджен Лайф Саєнсиз  Лімітед, Індія</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>відсутній</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr"/>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57" ht="40" customHeight="1">
-      <c r="A57" s="2" t="n">
-        <v>55</v>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>№ 345-001.001/002.0/17-26 від 28.07.2026</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>28.07.2026</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>ФІБРИНАЗА-10, таблетки, вкриті оболонкою, кишковорозчинні по 10 мг, по 10 таблеток у блістері; по 3 блістери у картонній пачці, Серія № ESI25011B1, ESI25012B1, ESI26002B1, ESI26003B1, Евертоджен Лайф Саєнсиз Лімітед, Індія</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>відсутній</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr"/>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58" ht="40" customHeight="1">
-      <c r="A58" s="2" t="n">
-        <v>56</v>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>№ 351-001.001/002.0/17-26 від 31.07.2026</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>31.07.2026</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>ДРОТАВЕРИНУ ГІДРОХЛОРИД, таблетки по 40 мг; по 10 таблеток у блістері; по 2 блістера в пачці з картону, Серія № 40126, АТ "Лубнифарм", Україна</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>відсутній</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr"/>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59" ht="40" customHeight="1">
-      <c r="A59" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>№ 353-001.001/002.0/17-26 від 31.07.2026</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>31.07.2026</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>всі серії ЛЗ виробництва LIANYUNGANG GUIKE PHARMACEUTICAL CO. LTD., -, Серія № всі серії, LIANYUNGANG GUIKE PHARMACEUTICAL CO. LTD., Китай</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>відсутній</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr"/>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12260,7 +12148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -13813,6 +13701,286 @@
       <c r="G54" s="2" t="inlineStr"/>
       <c r="H54" s="2" t="inlineStr"/>
     </row>
+    <row r="55" ht="40" customHeight="1">
+      <c r="A55" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>№ 528-001.1/002.1/17-26 від 23.10.2026</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>23.10.2026</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>ЛАМІКТАЛ, таблетки, що диспергуються, по 50 мг; по 14 таблеток у блістері з полівінілхлориду/полівінілденхлориду/паперу/алюмінієвої фольги із захистом від відкривання дітьми; по 2 блістери в картонній коробці, Серія № FTKG, Делфарм Познань С.А., Польща</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr"/>
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56" ht="40" customHeight="1">
+      <c r="A56" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>№ 528-001.1/002.1/17-26 від 23.10.2026</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>23.10.2026</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>ЛАМІКТАЛ, таблетки,що диспергуються,по100мг; по14таблеток у блістері з полівінілхлориду/полівінілденхлориду/паперу/алюмінієвої фольги із захистом від відкривання дітьми; по 2 блістери в картонній коробці, Серія № FKRM, Делфарм Познань С.А., Польща</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr"/>
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57" ht="40" customHeight="1">
+      <c r="A57" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>№ 531-001.1/002.1/17-26 від 23.10.2026</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>23.10.2026</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>OLFEN  MAX (Diclofenacum natricum), 20 мг/г, гель в тубі 50 г, Серія № C51789A, C51790A, Merckle GmbH, Німеччина</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr"/>
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58" ht="40" customHeight="1">
+      <c r="A58" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>№ 531-001.1/002.1/17-26 від 23.10.2026</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>23.10.2026</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>OLFEN  MAX (Diclofenacum natricum), 20 мг/г, гель в тубі 100 г, Серія № B72256A, B72257A, B72688A, B72475A, B72476A, B72563A, B72562A, B72687A, B72255A, С53995A, С53834A, С53835A, С54087A, С54088A, С53996A, С54216A, С54215A, С54217A., Merckle GmbH, Німеччина</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr"/>
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59" ht="40" customHeight="1">
+      <c r="A59" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>№ 531-001.1/002.1/17-26 від 23.10.2026</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>23.10.2026</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>OLFEN  MAX (Diclofenacum natricum), 20 мг/г, гель в тубі 150 г, Серія № B70993C, B70994A, C53137A, C53136B, C53039B, Merckle GmbH, Німеччина</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr"/>
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60" ht="40" customHeight="1">
+      <c r="A60" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>№ 532-001.1/002.1/17-26 від 23.10.2026</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>23.10.2026</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>KRABEVA  400 mg  (Bevacizumab), 25 mg/ml, Концентрат для розчину для інфузій у флаконі, Серія № BF25008690, Biocon Limited India, Індія</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr"/>
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61" ht="40" customHeight="1">
+      <c r="A61" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>№ 533-001.1/002.1/17-26 від 23.10.2026</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>23.10.2026</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>BALFUMON (Dimethylis fumaras),120 mg, тверді капсули з кишковорозчинним покриттям №14, Серія № 25991006, Sanovel Ilac San. ve Tic. A.S., Туреччина</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr"/>
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62" ht="40" customHeight="1">
+      <c r="A62" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>№ 534-001.1/002.1/17-26 від 23.10.2026</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>23.10.2026</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>CIALIS (Tadalafil), 5 mg, таблетки вкриті плівковою оболонкою № 28, Серія № D641573, з маркуванням виробника  Lilly del Caribe Inc. Carolina, Puerto Rico, США</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr"/>
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63" ht="40" customHeight="1">
+      <c r="A63" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>№ 535-001.1/002.1/17-26 від 23.10.2026</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>23.10.2026</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>XEOMIN (Botulinum toxin A), 100U, асіептично оброблені парентеральні розчини малих об’ємів, Серія № NDC 46785-162-03, MERZ PHARMA GMBH &amp; CO. KGAA, Німеччина</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr"/>
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64" ht="40" customHeight="1">
+      <c r="A64" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>№ 536-001.1/002.1/17-26 від 23.10.2026</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>23.10.2026</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>DYSPORT 500U (BotulinumToxin  type A), ліофілізований порошок, Серія № 025155, IPSEN BIOPHARM LTD., -</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr"/>
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/Журнал_ДЛС.xlsx
+++ b/data/Журнал_ДЛС.xlsx
@@ -12148,7 +12148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -13981,6 +13981,62 @@
       <c r="G64" s="2" t="inlineStr"/>
       <c r="H64" s="2" t="inlineStr"/>
     </row>
+    <row r="65" ht="40" customHeight="1">
+      <c r="A65" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>№ 537-001.3/002.1/17-26 від 29.10.2026</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>29.10.2026</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>DYSPORT®500 (Clostridium Botulinum tIP-A toksin), 500 unit/vial, Серія № 029035 (термін придатності - 09/2027), Р09608  (термін придатності - 09/2028), з маркуванням виробника  Ipsen Biopharm Ltd, -</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr"/>
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66" ht="40" customHeight="1">
+      <c r="A66" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>№ 538-001.3/002.1/17-26 від 29.10.2026</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>29.10.2026</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>ОКОМІСТИН®, краплі очні/вушні/для носа, розчин 0,01 %; по 5 мл у флаконі полімерному з крапельницею; по 1 флакону в пачці з картону, Серія № 60824, АТ "Фармак", Україна</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>відсутній</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr"/>
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
